--- a/data/trans_bre/IP04D$colectiva-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Provincia-trans_bre.xlsx
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,23</t>
+          <t>-0,92; 6,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 1,53</t>
+          <t>-5,87; 1,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 2,29</t>
+          <t>-4,51; 1,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,05</t>
+          <t>-3,11; 1,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,41</t>
+          <t>-2,3; 4,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 271,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -792,17 +792,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 4,7</t>
+          <t>-1,95; 5,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 5,95</t>
+          <t>-3,81; 5,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 4,83</t>
+          <t>-16,2; 4,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-67,85; 46,77</t>
+          <t>-68,38; 37,86</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 11,49</t>
+          <t>-1,19; 11,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 4,94</t>
+          <t>-6,99; 4,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 17,39</t>
+          <t>0,73; 17,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,61; 1095,35</t>
+          <t>-51,82; 1150,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,28; 219,02</t>
+          <t>-77,58; 223,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 1295,78</t>
+          <t>-7,34; 1064,23</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 7,31</t>
+          <t>-16,33; 7,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-77,06; 111,89</t>
+          <t>-79,03; 91,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1032,39 +1032,39 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 10,59</t>
+          <t>-3,43; 9,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 11,18</t>
+          <t>-12,17; 11,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 22,16</t>
+          <t>-8,14; 22,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-72,48; 851,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,27; 81,04</t>
+          <t>-46,83; 81,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 79,36</t>
+          <t>-18,66; 76,9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1112,17 +1112,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 4,02</t>
+          <t>-0,3; 4,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,19</t>
+          <t>-2,93; 4,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 8,1</t>
+          <t>-4,58; 7,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-66,22; 256,32</t>
+          <t>-61,73; 301,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-41,82; 139,2</t>
+          <t>-40,74; 132,48</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,05</t>
+          <t>-2,95; 2,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,22</t>
+          <t>-1,22; 2,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,0</t>
+          <t>-1,76; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-80,84; 192,73</t>
+          <t>-76,93; 239,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,22</t>
+          <t>-0,74; 2,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,54</t>
+          <t>-1,76; 1,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,37</t>
+          <t>-1,51; 3,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 98,45</t>
+          <t>-22,76; 108,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-39,14; 53,53</t>
+          <t>-40,08; 53,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 56,01</t>
+          <t>-20,58; 55,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$colectiva-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Provincia-trans_bre.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 6,13</t>
+          <t>-1,14; 5,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 1,53</t>
+          <t>-5,5; 1,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 1,61</t>
+          <t>-4,02; 2,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,09</t>
+          <t>-3,18; 0,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 4,92</t>
+          <t>-2,57; 4,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 326,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -792,17 +792,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 5,21</t>
+          <t>-1,94; 5,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 5,02</t>
+          <t>-3,75; 5,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 4,01</t>
+          <t>-16,92; 4,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,38; 37,86</t>
+          <t>-68,48; 35,39</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 11,64</t>
+          <t>-1,65; 11,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 4,75</t>
+          <t>-6,99; 5,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 17,58</t>
+          <t>0,64; 18,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,82; 1150,02</t>
+          <t>-63,94; 1218,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,58; 223,33</t>
+          <t>-76,96; 290,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 1064,23</t>
+          <t>-18,46; 1169,82</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 7,25</t>
+          <t>-16,14; 7,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-79,03; 91,55</t>
+          <t>-79,56; 104,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 9,93</t>
+          <t>-3,55; 10,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 11,32</t>
+          <t>-13,34; 11,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 22,41</t>
+          <t>-6,64; 22,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,45; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 81,15</t>
+          <t>-49,5; 85,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 76,9</t>
+          <t>-15,28; 79,95</t>
         </is>
       </c>
     </row>
@@ -1112,17 +1112,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,36</t>
+          <t>-0,42; 4,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 4,66</t>
+          <t>-3,15; 4,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 7,63</t>
+          <t>-5,03; 7,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 301,73</t>
+          <t>-63,35; 250,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,74; 132,48</t>
+          <t>-42,14; 127,11</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,32</t>
+          <t>-3,06; 2,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,3</t>
+          <t>-1,29; 2,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,0</t>
+          <t>-2,48; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-76,93; 239,5</t>
+          <t>-77,49; 206,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,31</t>
+          <t>-0,69; 2,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,55</t>
+          <t>-1,76; 1,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,29</t>
+          <t>-1,32; 3,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 108,39</t>
+          <t>-22,18; 96,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-40,08; 53,79</t>
+          <t>-38,89; 53,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 55,47</t>
+          <t>-16,81; 54,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$colectiva-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Provincia-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción colectiva en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-44,66%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -632,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,89</t>
+          <t>-0,94; 5,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -642,7 +644,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 1,48</t>
+          <t>-1,54; 2,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -712,22 +714,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 2,46</t>
+          <t>-4,1; 2,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,99</t>
+          <t>-3,53; 1,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 4,25</t>
+          <t>-2,63; 5,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 326,17</t>
+          <t>-100,0; 271,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,05</t>
+          <t>-5,72</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-33,22%</t>
+          <t>-31,32%</t>
         </is>
       </c>
     </row>
@@ -792,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,22</t>
+          <t>-1,96; 4,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,1</t>
+          <t>-3,78; 5,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 4,42</t>
+          <t>-15,91; 5,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -817,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,48; 35,39</t>
+          <t>-66,71; 47,68</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,25</t>
+          <t>8,23</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>185,65%</t>
+          <t>172,94%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 11,79</t>
+          <t>-1,98; 11,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 5,42</t>
+          <t>-7,24; 4,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 18,58</t>
+          <t>0,88; 18,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 1218,84</t>
+          <t>-54,61; 1095,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,96; 290,89</t>
+          <t>-79,28; 219,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 1169,82</t>
+          <t>-14,2; 1244,06</t>
         </is>
       </c>
     </row>
@@ -952,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 7,33</t>
+          <t>-15,79; 7,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -967,7 +969,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-79,56; 104,48</t>
+          <t>-77,06; 111,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,79</t>
+          <t>8,34</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1019,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 10,69</t>
+          <t>-3,42; 10,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 11,23</t>
+          <t>-14,2; 11,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 22,95</t>
+          <t>-6,97; 22,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-74,45; —</t>
+          <t>-72,48; 851,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,5; 85,76</t>
+          <t>-54,27; 81,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 79,95</t>
+          <t>-15,63; 82,39</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1099,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -1112,17 +1114,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 4,5</t>
+          <t>-0,42; 4,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 4,45</t>
+          <t>-3,62; 4,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 7,41</t>
+          <t>-4,9; 8,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1132,12 +1134,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-63,35; 250,67</t>
+          <t>-66,22; 256,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-42,14; 127,11</t>
+          <t>-41,35; 129,63</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1192,22 +1194,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 2,26</t>
+          <t>-3,2; 2,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,35</t>
+          <t>-1,21; 2,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,0</t>
+          <t>-1,67; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-77,49; 206,66</t>
+          <t>-80,84; 192,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1244,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1259,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,18</t>
+          <t>-0,71; 2,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,44</t>
+          <t>-1,65; 1,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,39</t>
+          <t>-0,86; 4,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 96,86</t>
+          <t>-22,07; 98,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 53,49</t>
+          <t>-39,14; 53,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 54,31</t>
+          <t>-11,29; 70,32</t>
         </is>
       </c>
     </row>
